--- a/results/feature_selection/induction/wrapper/qP_calc/metrics_global.xlsx
+++ b/results/feature_selection/induction/wrapper/qP_calc/metrics_global.xlsx
@@ -488,118 +488,118 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>elasticnet_b</t>
+          <t>knn</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>t, P, T, I, Plag1, dVdt_calc</t>
+          <t>t_ind_ad, V_calc, Xlag1_calc</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0.8953155030603848</v>
+        <v>0.7738055871076852</v>
       </c>
       <c r="E2" t="n">
-        <v>0.001473344043641112</v>
+        <v>0.00175815801404918</v>
       </c>
       <c r="F2" t="n">
-        <v>4.990637052446091e-06</v>
+        <v>1.0783394399725e-05</v>
       </c>
       <c r="G2" t="n">
-        <v>0.002233973377738887</v>
+        <v>0.003283807911514466</v>
       </c>
       <c r="H2" t="n">
-        <v>545.45609937057</v>
+        <v>511.4073668232957</v>
       </c>
       <c r="I2" t="n">
-        <v>0.03440884252782129</v>
+        <v>0.06936587224377425</v>
       </c>
       <c r="J2" t="n">
-        <v>-647.2291374885431</v>
+        <v>-611.6251707840036</v>
       </c>
       <c r="K2" t="n">
-        <v>-635.2952332091575</v>
+        <v>-605.6582186443108</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Ridge_b</t>
+          <t>tweedie</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>t, P, Plag1</t>
+          <t>t, t_ind_ad, I, FS_calc</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.8787820579547742</v>
+        <v>0.5775876635030719</v>
       </c>
       <c r="E3" t="n">
-        <v>0.001568950367814557</v>
+        <v>0.002438671690145937</v>
       </c>
       <c r="F3" t="n">
-        <v>5.778838038846581e-06</v>
+        <v>2.013771589453123e-05</v>
       </c>
       <c r="G3" t="n">
-        <v>0.002403921387825854</v>
+        <v>0.004487506645625299</v>
       </c>
       <c r="H3" t="n">
-        <v>378.3534769594864</v>
+        <v>1180.171369723459</v>
       </c>
       <c r="I3" t="n">
-        <v>0.03786942780019496</v>
+        <v>0.1287377973502046</v>
       </c>
       <c r="J3" t="n">
-        <v>-645.3106280488696</v>
+        <v>-575.8974687789514</v>
       </c>
       <c r="K3" t="n">
-        <v>-639.3436759091768</v>
+        <v>-567.9415325926943</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>tweedie</t>
+          <t>elasticnet_b</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>t, P, T, I, Plag1, V_calc</t>
+          <t>T, FS_calc, V_calc</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.8778355583592925</v>
+        <v>0.4112456362703898</v>
       </c>
       <c r="E4" t="n">
-        <v>0.001469857108906796</v>
+        <v>0.003022988422323086</v>
       </c>
       <c r="F4" t="n">
-        <v>5.823960631870653e-06</v>
+        <v>2.806776006301278e-05</v>
       </c>
       <c r="G4" t="n">
-        <v>0.002413288344121078</v>
+        <v>0.005297901477284451</v>
       </c>
       <c r="H4" t="n">
-        <v>612.1819736648559</v>
+        <v>687.5119845229873</v>
       </c>
       <c r="I4" t="n">
-        <v>0.03965340926465457</v>
+        <v>0.1781459565509272</v>
       </c>
       <c r="J4" t="n">
-        <v>-638.8906203634378</v>
+        <v>-559.9680043275358</v>
       </c>
       <c r="K4" t="n">
-        <v>-626.9567160840522</v>
+        <v>-554.001052187843</v>
       </c>
     </row>
     <row r="5">
@@ -609,192 +609,192 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>t, P, I, Plag1</t>
+          <t>T, FS_calc, V_calc</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.8281261346375141</v>
+        <v>0.367261813457551</v>
       </c>
       <c r="E5" t="n">
-        <v>0.001775586261568989</v>
+        <v>0.002963233227906507</v>
       </c>
       <c r="F5" t="n">
-        <v>8.193764176179132e-06</v>
+        <v>3.016460632253671e-05</v>
       </c>
       <c r="G5" t="n">
-        <v>0.002862475183504502</v>
+        <v>0.005492231452018087</v>
       </c>
       <c r="H5" t="n">
-        <v>536.8569573739757</v>
+        <v>728.4212727197232</v>
       </c>
       <c r="I5" t="n">
-        <v>0.05356789524366912</v>
+        <v>0.1913425711871605</v>
       </c>
       <c r="J5" t="n">
-        <v>-624.4554066030032</v>
+        <v>-556.077430035808</v>
       </c>
       <c r="K5" t="n">
-        <v>-616.4994704167461</v>
+        <v>-550.1104778961152</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>rf_b</t>
+          <t>Ridge_b</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>t_ind, t_ind_ad</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.7890712182041013</v>
+        <v>0.2613059098040598</v>
       </c>
       <c r="E6" t="n">
-        <v>0.002264532348330164</v>
+        <v>0.003641316537605243</v>
       </c>
       <c r="F6" t="n">
-        <v>1.00556340683868e-05</v>
+        <v>3.521585530550255e-05</v>
       </c>
       <c r="G6" t="n">
-        <v>0.003171061978010963</v>
+        <v>0.00593429484484067</v>
       </c>
       <c r="H6" t="n">
-        <v>942.8808408773314</v>
+        <v>1723.833941495077</v>
       </c>
       <c r="I6" t="n">
-        <v>0.06378567348261749</v>
+        <v>0.222632878157496</v>
       </c>
       <c r="J6" t="n">
-        <v>-619.3983837428381</v>
+        <v>-549.7167636658464</v>
       </c>
       <c r="K6" t="n">
-        <v>-617.4093996962738</v>
+        <v>-545.7387955727179</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>knn</t>
+          <t>poisson</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>t_ind_ad, I, V_calc</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.7625556468090905</v>
+        <v>0.2250684571268298</v>
       </c>
       <c r="E7" t="n">
-        <v>0.00257858842321056</v>
+        <v>0.003287474194098452</v>
       </c>
       <c r="F7" t="n">
-        <v>1.131971420383467e-05</v>
+        <v>3.694340789737834e-05</v>
       </c>
       <c r="G7" t="n">
-        <v>0.003364478295937524</v>
+        <v>0.006078108907989255</v>
       </c>
       <c r="H7" t="n">
-        <v>1154.101817673923</v>
+        <v>2287.798294322648</v>
       </c>
       <c r="I7" t="n">
-        <v>0.07174122975721556</v>
+        <v>0.2340053232474792</v>
       </c>
       <c r="J7" t="n">
-        <v>-613.0040955560271</v>
+        <v>-545.1306599556077</v>
       </c>
       <c r="K7" t="n">
-        <v>-611.0151115094628</v>
+        <v>-539.1637078159149</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>poisson</t>
+          <t>svm_rbf</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>t_ind, t_ind_ad</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0.6982071176277438</v>
+        <v>0.1968583871926066</v>
       </c>
       <c r="E8" t="n">
-        <v>0.002401955001719025</v>
+        <v>0.004845979516614818</v>
       </c>
       <c r="F8" t="n">
-        <v>1.438740964481367e-05</v>
+        <v>3.82882700725965e-05</v>
       </c>
       <c r="G8" t="n">
-        <v>0.003793073904475586</v>
+        <v>0.006187751616911954</v>
       </c>
       <c r="H8" t="n">
-        <v>848.6874292106153</v>
+        <v>1897.61841149801</v>
       </c>
       <c r="I8" t="n">
-        <v>0.09104793589842824</v>
+        <v>0.2419692856312689</v>
       </c>
       <c r="J8" t="n">
-        <v>-600.0544814588728</v>
+        <v>-545.1998165479005</v>
       </c>
       <c r="K8" t="n">
-        <v>-598.0654974123086</v>
+        <v>-541.2218484547719</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>linear</t>
+          <t>rf_b</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>t, t_ind_ad, FS_calc, V_calc, mu_calc</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0.6949336871942806</v>
+        <v>0.1152989289817069</v>
       </c>
       <c r="E9" t="n">
-        <v>0.002915231196537721</v>
+        <v>0.003045804103642918</v>
       </c>
       <c r="F9" t="n">
-        <v>1.454346430130467e-05</v>
+        <v>4.217646427540699e-05</v>
       </c>
       <c r="G9" t="n">
-        <v>0.003813589424846974</v>
+        <v>0.00649434094234411</v>
       </c>
       <c r="H9" t="n">
-        <v>1314.465846036701</v>
+        <v>646.9410165176618</v>
       </c>
       <c r="I9" t="n">
-        <v>0.09203007426672674</v>
+        <v>0.2679398448304808</v>
       </c>
       <c r="J9" t="n">
-        <v>-599.4719181255095</v>
+        <v>-533.9770033992609</v>
       </c>
       <c r="K9" t="n">
-        <v>-597.4829340789453</v>
+        <v>-524.0320831664395</v>
       </c>
     </row>
     <row r="10">
@@ -808,38 +808,38 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>P, FS_calc, Plag1</t>
+          <t>V_calc, dVdt_calc, Xlag1_calc</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0.1571903388705409</v>
+        <v>0.0585645899861601</v>
       </c>
       <c r="E10" t="n">
-        <v>0.00516392593862532</v>
+        <v>0.005320960498944986</v>
       </c>
       <c r="F10" t="n">
-        <v>4.017936987764707e-05</v>
+        <v>4.488116747993723e-05</v>
       </c>
       <c r="G10" t="n">
-        <v>0.006338719892663429</v>
+        <v>0.006699340824285418</v>
       </c>
       <c r="H10" t="n">
-        <v>3137.372756379611</v>
+        <v>1362.898890922572</v>
       </c>
       <c r="I10" t="n">
-        <v>0.2543710238977521</v>
+        <v>0.283962039821388</v>
       </c>
       <c r="J10" t="n">
-        <v>-540.5964715841567</v>
+        <v>-534.6205833209119</v>
       </c>
       <c r="K10" t="n">
-        <v>-534.6295194444639</v>
+        <v>-528.6536311812191</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>svm_rbf</t>
+          <t>linear</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -847,32 +847,32 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>FS_calc</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0.00767001558381819</v>
+        <v>-0.2832879981114338</v>
       </c>
       <c r="E11" t="n">
-        <v>0.006115584185832647</v>
+        <v>0.004769111203390929</v>
       </c>
       <c r="F11" t="n">
-        <v>4.730747086015325e-05</v>
+        <v>6.117834846193635e-05</v>
       </c>
       <c r="G11" t="n">
-        <v>0.00687804266198991</v>
+        <v>0.007821658932856659</v>
       </c>
       <c r="H11" t="n">
-        <v>3421.783047740959</v>
+        <v>1608.771997380397</v>
       </c>
       <c r="I11" t="n">
-        <v>0.2982321105544567</v>
+        <v>0.7710584485547072</v>
       </c>
       <c r="J11" t="n">
-        <v>-535.7774857462975</v>
+        <v>-521.8927295745633</v>
       </c>
       <c r="K11" t="n">
-        <v>-533.7885016997333</v>
+        <v>-519.903745527999</v>
       </c>
     </row>
     <row r="12">
@@ -882,36 +882,36 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>t_ind_ad, FS_calc</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>-0.4152100531019278</v>
+        <v>-0.4355414616210957</v>
       </c>
       <c r="E12" t="n">
-        <v>0.007696671848180188</v>
+        <v>0.007438574766150012</v>
       </c>
       <c r="F12" t="n">
-        <v>6.746748500953957e-05</v>
+        <v>6.843674677847854e-05</v>
       </c>
       <c r="G12" t="n">
-        <v>0.008213859324917829</v>
+        <v>0.00827265052921242</v>
       </c>
       <c r="H12" t="n">
-        <v>4153.375500397045</v>
+        <v>4183.362562222499</v>
       </c>
       <c r="I12" t="n">
-        <v>0.8502204863401702</v>
+        <v>0.8634206884181475</v>
       </c>
       <c r="J12" t="n">
-        <v>-516.6086981040484</v>
+        <v>-513.8384347754918</v>
       </c>
       <c r="K12" t="n">
-        <v>-514.6197140574841</v>
+        <v>-509.8604666823633</v>
       </c>
     </row>
   </sheetData>

--- a/results/feature_selection/induction/wrapper/qP_calc/metrics_global.xlsx
+++ b/results/feature_selection/induction/wrapper/qP_calc/metrics_global.xlsx
@@ -496,32 +496,32 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>t_ind_ad, V_calc, Xlag1_calc</t>
+          <t>t_ind_ad, X_calc, V_calc</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0.7738055871076852</v>
+        <v>0.7663491009177412</v>
       </c>
       <c r="E2" t="n">
-        <v>0.00175815801404918</v>
+        <v>0.001857721908925226</v>
       </c>
       <c r="F2" t="n">
-        <v>1.0783394399725e-05</v>
+        <v>1.113886839395026e-05</v>
       </c>
       <c r="G2" t="n">
-        <v>0.003283807911514466</v>
+        <v>0.003337494328676868</v>
       </c>
       <c r="H2" t="n">
-        <v>511.4073668232957</v>
+        <v>520.7502304078221</v>
       </c>
       <c r="I2" t="n">
-        <v>0.06936587224377425</v>
+        <v>0.0716030669325534</v>
       </c>
       <c r="J2" t="n">
-        <v>-611.6251707840036</v>
+        <v>-609.8737750892466</v>
       </c>
       <c r="K2" t="n">
-        <v>-605.6582186443108</v>
+        <v>-603.9068229495538</v>
       </c>
     </row>
     <row r="3">
@@ -644,7 +644,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Ridge_b</t>
+          <t>svm_rbf</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -652,188 +652,188 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>t_ind, t_ind_ad</t>
+          <t>t, t_ind_ad</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.2613059098040598</v>
+        <v>0.3513671398302681</v>
       </c>
       <c r="E6" t="n">
-        <v>0.003641316537605243</v>
+        <v>0.004265563444552982</v>
       </c>
       <c r="F6" t="n">
-        <v>3.521585530550255e-05</v>
+        <v>3.092235507674444e-05</v>
       </c>
       <c r="G6" t="n">
-        <v>0.00593429484484067</v>
+        <v>0.005560787271308302</v>
       </c>
       <c r="H6" t="n">
-        <v>1723.833941495077</v>
+        <v>1919.66283429533</v>
       </c>
       <c r="I6" t="n">
-        <v>0.222632878157496</v>
+        <v>0.1956115036994733</v>
       </c>
       <c r="J6" t="n">
-        <v>-549.7167636658464</v>
+        <v>-556.7376831999048</v>
       </c>
       <c r="K6" t="n">
-        <v>-545.7387955727179</v>
+        <v>-552.7597151067763</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>poisson</t>
+          <t>Ridge_b</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>t_ind_ad, I, V_calc</t>
+          <t>t, t_ind_ad</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.2250684571268298</v>
+        <v>0.2263934162664198</v>
       </c>
       <c r="E7" t="n">
-        <v>0.003287474194098452</v>
+        <v>0.003682238387292338</v>
       </c>
       <c r="F7" t="n">
-        <v>3.694340789737834e-05</v>
+        <v>3.688024295540198e-05</v>
       </c>
       <c r="G7" t="n">
-        <v>0.006078108907989255</v>
+        <v>0.006072910583517757</v>
       </c>
       <c r="H7" t="n">
-        <v>2287.798294322648</v>
+        <v>1863.946677314788</v>
       </c>
       <c r="I7" t="n">
-        <v>0.2340053232474792</v>
+        <v>0.2331077912901429</v>
       </c>
       <c r="J7" t="n">
-        <v>-545.1306599556077</v>
+        <v>-547.223066864767</v>
       </c>
       <c r="K7" t="n">
-        <v>-539.1637078159149</v>
+        <v>-543.2450987716385</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>svm_rbf</t>
+          <t>poisson</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>t_ind, t_ind_ad</t>
+          <t>t_ind_ad, I, V_calc</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0.1968583871926066</v>
+        <v>0.2250684571268298</v>
       </c>
       <c r="E8" t="n">
-        <v>0.004845979516614818</v>
+        <v>0.003287474194098452</v>
       </c>
       <c r="F8" t="n">
-        <v>3.82882700725965e-05</v>
+        <v>3.694340789737834e-05</v>
       </c>
       <c r="G8" t="n">
-        <v>0.006187751616911954</v>
+        <v>0.006078108907989255</v>
       </c>
       <c r="H8" t="n">
-        <v>1897.61841149801</v>
+        <v>2287.798294322648</v>
       </c>
       <c r="I8" t="n">
-        <v>0.2419692856312689</v>
+        <v>0.2340053232474792</v>
       </c>
       <c r="J8" t="n">
-        <v>-545.1998165479005</v>
+        <v>-545.1306599556077</v>
       </c>
       <c r="K8" t="n">
-        <v>-541.2218484547719</v>
+        <v>-539.1637078159149</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>rf_b</t>
+          <t>svm_linear</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>t, t_ind_ad, FS_calc, V_calc, mu_calc</t>
+          <t>t_ind_ad, T, FS_calc, V_calc</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0.1152989289817069</v>
+        <v>-0.08518846005454517</v>
       </c>
       <c r="E9" t="n">
-        <v>0.003045804103642918</v>
+        <v>0.005322339795684325</v>
       </c>
       <c r="F9" t="n">
-        <v>4.217646427540699e-05</v>
+        <v>5.173432452714649e-05</v>
       </c>
       <c r="G9" t="n">
-        <v>0.00649434094234411</v>
+        <v>0.007192657681771495</v>
       </c>
       <c r="H9" t="n">
-        <v>646.9410165176618</v>
+        <v>1293.713392591776</v>
       </c>
       <c r="I9" t="n">
-        <v>0.2679398448304808</v>
+        <v>0.6551855040870652</v>
       </c>
       <c r="J9" t="n">
-        <v>-533.9770033992609</v>
+        <v>-524.9470102871996</v>
       </c>
       <c r="K9" t="n">
-        <v>-524.0320831664395</v>
+        <v>-516.9910741009426</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>svm_linear</t>
+          <t>rf_b</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>V_calc, dVdt_calc, Xlag1_calc</t>
+          <t>FS_calc</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0.0585645899861601</v>
+        <v>-0.1699604706041347</v>
       </c>
       <c r="E10" t="n">
-        <v>0.005320960498944986</v>
+        <v>0.003387363783402719</v>
       </c>
       <c r="F10" t="n">
-        <v>4.488116747993723e-05</v>
+        <v>5.577567113745851e-05</v>
       </c>
       <c r="G10" t="n">
-        <v>0.006699340824285418</v>
+        <v>0.007468311130199284</v>
       </c>
       <c r="H10" t="n">
-        <v>1362.898890922572</v>
+        <v>519.6972610029133</v>
       </c>
       <c r="I10" t="n">
-        <v>0.283962039821388</v>
+        <v>0.7030543683020734</v>
       </c>
       <c r="J10" t="n">
-        <v>-534.6205833209119</v>
+        <v>-526.8853303777933</v>
       </c>
       <c r="K10" t="n">
-        <v>-528.6536311812191</v>
+        <v>-524.896346331229</v>
       </c>
     </row>
     <row r="11">
@@ -882,36 +882,36 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>t_ind_ad, FS_calc</t>
+          <t>FS_calc</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>-0.4355414616210957</v>
+        <v>-0.563368341553329</v>
       </c>
       <c r="E12" t="n">
-        <v>0.007438574766150012</v>
+        <v>0.006611380135606741</v>
       </c>
       <c r="F12" t="n">
-        <v>6.843674677847854e-05</v>
+        <v>7.453065353581206e-05</v>
       </c>
       <c r="G12" t="n">
-        <v>0.00827265052921242</v>
+        <v>0.008633113779848616</v>
       </c>
       <c r="H12" t="n">
-        <v>4183.362562222499</v>
+        <v>3089.508937808343</v>
       </c>
       <c r="I12" t="n">
-        <v>0.8634206884181475</v>
+        <v>0.9391253478469477</v>
       </c>
       <c r="J12" t="n">
-        <v>-513.8384347754918</v>
+        <v>-511.2322032587587</v>
       </c>
       <c r="K12" t="n">
-        <v>-509.8604666823633</v>
+        <v>-509.2432192121944</v>
       </c>
     </row>
   </sheetData>
